--- a/EventOption_事件选项表.xlsx
+++ b/EventOption_事件选项表.xlsx
@@ -158,7 +158,7 @@
     <t>1003</t>
   </si>
   <si>
-    <t>赏他物资</t>
+    <t>接过他的物资</t>
   </si>
   <si>
     <t>6</t>
@@ -191,10 +191,10 @@
     <t>1005</t>
   </si>
   <si>
-    <t>给他口粮</t>
-  </si>
-  <si>
-    <t>让他留下</t>
+    <t>接过他的补给</t>
+  </si>
+  <si>
+    <t>收下他的图纸</t>
   </si>
 </sst>
 </file>
